--- a/data/attendance/ECOLE_بن_يحي_2_ثانوي.xlsx
+++ b/data/attendance/ECOLE_بن_يحي_2_ثانوي.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
   <si>
     <t>بن يحي 2 ثانوي  |  ECOLE  |  2AS  |  بن يحيى عبد النور</t>
   </si>
@@ -85,6 +85,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -145,7 +151,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -661,7 +670,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -671,10 +680,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -716,46 +728,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -763,7 +775,7 @@
         <v>721</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -807,7 +819,7 @@
         <v>726</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -851,7 +863,7 @@
         <v>740</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -895,7 +907,7 @@
         <v>741</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -939,7 +951,7 @@
         <v>742</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -983,7 +995,7 @@
         <v>821</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1027,7 +1039,7 @@
         <v>822</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1082,7 +1094,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1090,77 +1102,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
